--- a/docs/downloads/compliance-officer-checklist.xlsx
+++ b/docs/downloads/compliance-officer-checklist.xlsx
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Compliance Officer  |  FSI Agent Governance Framework v1.2.41 — February 2026</t>
+          <t>Role: Compliance Officer  |  FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;CCompliance Officer Checklist</oddHeader>
-    <oddFooter>&amp;CFSI Agent Governance Framework v1.2.41 — February 2026</oddFooter>
+    <oddFooter>&amp;CFSI Agent Governance Framework v1.3.0 — March 2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/docs/downloads/compliance-officer-checklist.xlsx
+++ b/docs/downloads/compliance-officer-checklist.xlsx
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Compliance Officer  |  FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>Role: Compliance Officer  |  FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>
@@ -806,10 +806,11 @@
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="11" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/compliance-officer-checklist.xlsx
+++ b/docs/downloads/compliance-officer-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Compliance Officer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Officer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Compliance Officer'!$A$4:$E$4</definedName>
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Compliance Officer  |  FSI Agent Governance Framework v1.4.0 — April 2026</t>
+          <t>Role: Compliance Officer  |  FSI Agent Governance Framework v1.6.2 — May 2026</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Model Risk Management (OCC 2011-12 / SR 11-7)</t>
+          <t>Model Risk Management (OCC Bulletin 2026-13 / Fed SR 26-2)</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
+          <t>FSI Agent Governance Framework v1.6.2 — May 2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/compliance-officer-checklist.xlsx
+++ b/docs/downloads/compliance-officer-checklist.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Model Risk Management (OCC Bulletin 2026-13 / Fed SR 26-2)</t>
+          <t>Model Risk Management (Alignment with OCC Bulletin 2026-13 (formerly OCC 2011-12) / Fed SR 26-2 (formerly SR 11-7))</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
